--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R3d29052f64244ed8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R4d78ab0a06764541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R089c3834c70c4f95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Re85c458008b74bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R981b01dff07a4878"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="Rf127a78f2fd741fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R05133bb88a824314"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R376cde7cf2224527"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R3347c811bb95471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R2c96d3fd9fcd492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R9b09b39fffaa4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R7e93171542f44006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rd9ab73b1cdea444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R884879ca246142ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rb11a496f3abe41bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Rf5a3ba30710245df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R7ae3f22be3774901"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R19178e2ac0a14b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R736da7f70fee42eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rb4d32044c45c4a44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R7f0514c5f3c44b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R62600f764dd4447e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1037,7 +1037,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.0</x:v>
+        <x:v>v5.2.1</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10268,7 +10268,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.0</x:v>
+        <x:v>5.2.1</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R7e93171542f44006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rd9ab73b1cdea444d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R884879ca246142ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rb11a496f3abe41bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Rf5a3ba30710245df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R7ae3f22be3774901"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R19178e2ac0a14b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R736da7f70fee42eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rb4d32044c45c4a44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R7f0514c5f3c44b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R62600f764dd4447e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R07c4acc866544826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R7192e7a5360b4c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Rca9b5b5cc33c454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rf1fedf0277f14437"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R4b6bfe4c886c40a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R539f955c24664003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R25bd3ffc6f014306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="Rae290a7e04e44dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R42f17a104fb84a93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R3c901a5527a1409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="Rd9396f95f3a14362"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1037,7 +1037,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.1</x:v>
+        <x:v>v5.2.2</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10268,7 +10268,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.1</x:v>
+        <x:v>5.2.2</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R07c4acc866544826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R7192e7a5360b4c8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Rca9b5b5cc33c454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rf1fedf0277f14437"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R4b6bfe4c886c40a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R539f955c24664003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R25bd3ffc6f014306"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="Rae290a7e04e44dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R42f17a104fb84a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R3c901a5527a1409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="Rd9396f95f3a14362"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R3d936406f2eb494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R782e3a5122214eaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R9952f695c3ac42f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rde813a469c3e4648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R6583c9db18ea437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R5b3002288f1a43fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R8945b554c5b14e2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R83afe2da92a346a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rc2f2857eb41a4d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R878fdea876df4c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="Rc48b146b91bb4909"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1037,7 +1037,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.2</x:v>
+        <x:v>v5.2.3</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10268,7 +10268,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.2</x:v>
+        <x:v>5.2.3</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R3d936406f2eb494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R782e3a5122214eaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R9952f695c3ac42f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rde813a469c3e4648"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R6583c9db18ea437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R5b3002288f1a43fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R8945b554c5b14e2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R83afe2da92a346a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rc2f2857eb41a4d34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R878fdea876df4c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="Rc48b146b91bb4909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R7b18ee336f3a4193"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R876aac2801b943bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R34ed1749e2f64dbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="R7c793fc3e8bf4ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R971782d6f550400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R79e078d6efa447f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R366d65e53ded4ca4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R200335c2d82144b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rb02a6716dca84ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R1462a67e34ca4b05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="Re2868302d19341e8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1037,7 +1037,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.3</x:v>
+        <x:v>v5.2.4</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10268,7 +10268,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.3</x:v>
+        <x:v>5.2.4</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R7b18ee336f3a4193"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R876aac2801b943bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R34ed1749e2f64dbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="R7c793fc3e8bf4ebf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R971782d6f550400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R79e078d6efa447f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R366d65e53ded4ca4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R200335c2d82144b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rb02a6716dca84ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R1462a67e34ca4b05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="Re2868302d19341e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="Re75220db6ffc44bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rb947357db1d94f9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Rcff38ebb448249a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rfd4b7b3e3978428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R522ede228c674a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R74b2dc9f5fc443b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R461f5767a9c643fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R2ee719bfa4d74b5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rcfae0354912e442c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R75f0dfc06e70456a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R3a2a97d88dc743bc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1037,7 +1037,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.4</x:v>
+        <x:v>v5.2.5</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -6339,52 +6339,97 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="74" t="str">
+        <x:v>選択</x:v>
+      </x:c>
+      <x:c r="B1" s="74" t="str">
+        <x:v>改善実施日</x:v>
+      </x:c>
+      <x:c r="C1" s="74" t="str">
+        <x:v>経過日数</x:v>
+      </x:c>
+      <x:c r="D1" s="74" t="str">
+        <x:v>次回測定予定日</x:v>
+      </x:c>
+      <x:c r="E1" s="74" t="str">
+        <x:v>測定回数</x:v>
+      </x:c>
+      <x:c r="F1" s="74" t="str">
         <x:v>記事タイトル</x:v>
       </x:c>
-      <x:c r="B1" s="74" t="str">
-        <x:v>URL</x:v>
-      </x:c>
-      <x:c r="C1" s="74" t="str">
-        <x:v>改善日</x:v>
-      </x:c>
-      <x:c r="D1" s="74" t="str">
-        <x:v>改善内容</x:v>
-      </x:c>
-      <x:c r="E1" s="74" t="str">
-        <x:v>修正内容</x:v>
-      </x:c>
-      <x:c r="F1" s="74" t="str">
+      <x:c r="G1" s="74" t="str">
+        <x:v>改善前CTR</x:v>
+      </x:c>
+      <x:c r="H1" s="74" t="str">
+        <x:v>現在CTR</x:v>
+      </x:c>
+      <x:c r="I1" s="74" t="str">
         <x:v>改善前順位</x:v>
       </x:c>
-      <x:c r="G1" s="74" t="str">
+      <x:c r="J1" s="74" t="str">
         <x:v>現在順位</x:v>
       </x:c>
-      <x:c r="H1" s="74" t="str">
+      <x:c r="K1" s="74" t="str">
+        <x:v>判定</x:v>
+      </x:c>
+      <x:c r="L1" s="74" t="str">
+        <x:v>ArticleID</x:v>
+      </x:c>
+      <x:c r="M1" s="74" t="str">
+        <x:v>記事URL</x:v>
+      </x:c>
+      <x:c r="N1" s="74" t="str">
+        <x:v>改善概要</x:v>
+      </x:c>
+      <x:c r="O1" s="77" t="str">
+        <x:v>変更箇所</x:v>
+      </x:c>
+      <x:c r="P1" s="77" t="str">
+        <x:v>改善前クリック</x:v>
+      </x:c>
+      <x:c r="Q1" t="str">
+        <x:v>現在クリック</x:v>
+      </x:c>
+      <x:c r="R1" t="str">
+        <x:v>クリック変化</x:v>
+      </x:c>
+      <x:c r="S1" t="str">
+        <x:v>改善前表示回数</x:v>
+      </x:c>
+      <x:c r="T1" t="str">
+        <x:v>現在表示回数</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>表示回数変化</x:v>
+      </x:c>
+      <x:c r="V1" t="str">
+        <x:v>CTR変化</x:v>
+      </x:c>
+      <x:c r="W1" t="str">
         <x:v>順位変化</x:v>
       </x:c>
-      <x:c r="I1" s="74" t="str">
-        <x:v>改善前CTR</x:v>
-      </x:c>
-      <x:c r="J1" s="74" t="str">
-        <x:v>現在CTR</x:v>
-      </x:c>
-      <x:c r="K1" s="74" t="str">
-        <x:v>CTR変化</x:v>
-      </x:c>
-      <x:c r="L1" s="74" t="str">
-        <x:v>改善前クリック</x:v>
-      </x:c>
-      <x:c r="M1" s="74" t="str">
-        <x:v>現在クリック</x:v>
-      </x:c>
-      <x:c r="N1" s="74" t="str">
-        <x:v>クリック変化</x:v>
-      </x:c>
-      <x:c r="O1" s="77" t="str">
-        <x:v>判定</x:v>
-      </x:c>
-      <x:c r="P1" s="77" t="str">
-        <x:v>コメント</x:v>
+      <x:c r="X1" t="str">
+        <x:v>期待CTR効果</x:v>
+      </x:c>
+      <x:c r="Y1" t="str">
+        <x:v>期待クリック効果</x:v>
+      </x:c>
+      <x:c r="Z1" t="str">
+        <x:v>SIMS評価</x:v>
+      </x:c>
+      <x:c r="AA1" t="str">
+        <x:v>次のアクション</x:v>
+      </x:c>
+      <x:c r="AB1" t="str">
+        <x:v>測定コメント</x:v>
+      </x:c>
+      <x:c r="AC1" t="str">
+        <x:v>最新測定日時</x:v>
+      </x:c>
+      <x:c r="AD1" t="str">
+        <x:v>測定状態</x:v>
+      </x:c>
+      <x:c r="AE1" t="str">
+        <x:v>改善履歴ID</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -10268,7 +10313,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.4</x:v>
+        <x:v>5.2.5</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="Re75220db6ffc44bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rb947357db1d94f9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Rcff38ebb448249a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rfd4b7b3e3978428e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R522ede228c674a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R74b2dc9f5fc443b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R461f5767a9c643fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R2ee719bfa4d74b5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rcfae0354912e442c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R75f0dfc06e70456a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R3a2a97d88dc743bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R43393674f8554b01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R120b3a3134a24cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Red118ebf1f8d4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="R4624301be4ed4786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Rb23313f6b54d4b17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R9d5f730ddc9644ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R4086edb76a824d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R35b0da8fa23442bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R75ed1d32154241bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R56ab31c4e22542c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R49e489822fbb4748"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -23,6 +23,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy/M/d"/>
+  </x:numFmts>
   <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
@@ -357,7 +360,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="188">
+  <x:cellXfs count="189">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -859,6 +862,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="12" fillId="51" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="right" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1037,7 +1043,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.5</x:v>
+        <x:v>v5.2.6</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -6341,13 +6347,13 @@
       <x:c r="A1" s="74" t="str">
         <x:v>選択</x:v>
       </x:c>
-      <x:c r="B1" s="74" t="str">
+      <x:c r="B1" s="188" t="str">
         <x:v>改善実施日</x:v>
       </x:c>
       <x:c r="C1" s="74" t="str">
         <x:v>経過日数</x:v>
       </x:c>
-      <x:c r="D1" s="74" t="str">
+      <x:c r="D1" s="188" t="str">
         <x:v>次回測定予定日</x:v>
       </x:c>
       <x:c r="E1" s="74" t="str">
@@ -10313,7 +10319,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.5</x:v>
+        <x:v>5.2.6</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R43393674f8554b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R120b3a3134a24cdc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Red118ebf1f8d4629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="R4624301be4ed4786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Rb23313f6b54d4b17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R9d5f730ddc9644ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R4086edb76a824d99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R35b0da8fa23442bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R75ed1d32154241bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R56ab31c4e22542c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R49e489822fbb4748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R7f2cebf06d6e4ccb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rb20c06bfb16f481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R5c4c450ad3264835"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rde413d170099495e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R0cfa8fdfd2d04a9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R0a5d30d232684e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R3663e6a92fb147d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="Rf80c25623ab9499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R17b3bd276b4c4776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R20926bed42d2441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R6cd7f7e7557447c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -360,7 +360,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="189">
+  <x:cellXfs count="190">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -865,6 +865,9 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1043,7 +1046,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.6</x:v>
+        <x:v>v5.2.7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -6353,7 +6356,7 @@
       <x:c r="C1" s="74" t="str">
         <x:v>経過日数</x:v>
       </x:c>
-      <x:c r="D1" s="188" t="str">
+      <x:c r="D1" s="189" t="str">
         <x:v>次回測定予定日</x:v>
       </x:c>
       <x:c r="E1" s="74" t="str">
@@ -10319,7 +10322,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.6</x:v>
+        <x:v>5.2.7</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R7f2cebf06d6e4ccb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="Rb20c06bfb16f481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R5c4c450ad3264835"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rde413d170099495e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R0cfa8fdfd2d04a9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R0a5d30d232684e31"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R3663e6a92fb147d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="Rf80c25623ab9499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R17b3bd276b4c4776"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R20926bed42d2441b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R6cd7f7e7557447c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R83e3ceb948854a3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R900501f58bba4851"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R313f0840b99c43be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rd3b1d928963c4824"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Rfaa6bfca5f364105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R3a068e8a61514dce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R59902213357a44aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R74f77cd5feb44836"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rfa948dd33aba4ac2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R7a0a954de9534af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R670ebf3ee49e40d6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1046,7 +1046,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.7</x:v>
+        <x:v>v5.2.8</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10322,7 +10322,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.7</x:v>
+        <x:v>5.2.8</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R83e3ceb948854a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R900501f58bba4851"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R313f0840b99c43be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rd3b1d928963c4824"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Rfaa6bfca5f364105"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R3a068e8a61514dce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R59902213357a44aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R74f77cd5feb44836"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Rfa948dd33aba4ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R7a0a954de9534af1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R670ebf3ee49e40d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R00e5b74b38614fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R4f7c1fa9e6344b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Rcacd9a53b42f44b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rd7e37ab5216c400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Re20613f2633c491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="Rf597b680f582445c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R06c98a168a114655"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R6cb63affa682411e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Ra8ec31a7c6c04d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R35a5b4ae8a2b448c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R9c203a51ebcd4061"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1046,7 +1046,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.8</x:v>
+        <x:v>v5.2.9</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10322,7 +10322,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.8</x:v>
+        <x:v>5.2.9</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>

--- a/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
+++ b/spreadsheet/SIMS-Blog-Manager-template-Product5.2-Official.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="R00e5b74b38614fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R4f7c1fa9e6344b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="Rcacd9a53b42f44b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="Rd7e37ab5216c400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="Re20613f2633c491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="Rf597b680f582445c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R06c98a168a114655"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R6cb63affa682411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="Ra8ec31a7c6c04d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R35a5b4ae8a2b448c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R9c203a51ebcd4061"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ホーム" sheetId="1" r:id="Ra7c98fa8627542e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="今日の改善" sheetId="2" r:id="R72115a817fd644ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ログ" sheetId="3" r:id="R4e9a6e886b3b4075"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="セットアップ" sheetId="4" r:id="R1946e069c3b747f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善の推移" sheetId="5" r:id="R373c8149ba3d4306"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="改善ブリーフ" sheetId="6" r:id="R7b86fc0a03494555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="7" r:id="R91581e2e875c4a28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System_Log" sheetId="8" r:id="R53a35af608664518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="クエリデータ" sheetId="9" r:id="R6f1ea906cbc949ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事カルテ" sheetId="10" r:id="R2725887bb57f4182"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="記事診断" sheetId="11" r:id="R974a15014afa47f7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1046,7 +1046,7 @@
       <x:c r="F1" s="157"/>
       <x:c r="G1" s="157"/>
       <x:c r="H1" s="158" t="str">
-        <x:v>v5.2.9</x:v>
+        <x:v>v5.2.10</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
@@ -10322,7 +10322,7 @@
         <x:v>Version</x:v>
       </x:c>
       <x:c r="B2" s="28" t="str">
-        <x:v>5.2.9</x:v>
+        <x:v>5.2.10</x:v>
       </x:c>
       <x:c r="C2" s="28" t="str">
         <x:v>システムバージョン</x:v>
